--- a/SheepDemo/Luban/Configs/Datas/#LevelSort.xlsx
+++ b/SheepDemo/Luban/Configs/Datas/#LevelSort.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13965" windowHeight="13500"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="defaultSort" sheetId="3" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="44">
   <si>
     <t>##var</t>
   </si>
@@ -72,7 +72,10 @@
     <t>id</t>
   </si>
   <si>
-    <t>path</t>
+    <t>levelConfig</t>
+  </si>
+  <si>
+    <t>scene</t>
   </si>
   <si>
     <t>##type</t>
@@ -93,163 +96,106 @@
     <t>uniqueID</t>
   </si>
   <si>
-    <t>关卡索引</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>进门引导关</t>
-  </si>
-  <si>
-    <t>解锁引导关</t>
-  </si>
-  <si>
-    <t>推箱子引导关</t>
-  </si>
-  <si>
-    <t>密码门</t>
-  </si>
-  <si>
-    <t>气球飞走</t>
-  </si>
-  <si>
-    <t>绝处逢生</t>
-  </si>
-  <si>
-    <t>敲门</t>
-  </si>
-  <si>
-    <t>够不到钥匙</t>
-  </si>
-  <si>
-    <t>砸箱子拿钥匙</t>
-  </si>
-  <si>
-    <t>气球飞走2</t>
-  </si>
-  <si>
-    <t>相对运动</t>
-  </si>
-  <si>
-    <t>二段跳</t>
-  </si>
-  <si>
-    <t>垫脚石在哪？</t>
-  </si>
-  <si>
-    <t>错误的方向</t>
-  </si>
-  <si>
-    <t>水压过小</t>
-  </si>
-  <si>
-    <t>留下买路财【大狗】</t>
-  </si>
-  <si>
-    <t>遵守规则1</t>
-  </si>
-  <si>
-    <t>是时候逃走了【小狗】</t>
-  </si>
-  <si>
-    <t>噪音扰民</t>
-  </si>
-  <si>
-    <t>遵守规则2</t>
-  </si>
-  <si>
-    <t>开锁大师</t>
-  </si>
-  <si>
-    <t>奇怪的门</t>
-  </si>
-  <si>
-    <t>潜水1</t>
-  </si>
-  <si>
-    <t>伪装大师【大狗】</t>
-  </si>
-  <si>
-    <t>隐形砖</t>
-  </si>
-  <si>
-    <t>潜水2</t>
-  </si>
-  <si>
-    <t>下一关在哪</t>
-  </si>
-  <si>
-    <t>跑起来！</t>
-  </si>
-  <si>
-    <t>团结就是力量【大狗】</t>
-  </si>
-  <si>
-    <t>等级提升！</t>
-  </si>
-  <si>
-    <t>捣蛋鬼【牛角盒子】</t>
-  </si>
-  <si>
-    <t>金飞贼的秘密</t>
-  </si>
-  <si>
-    <t>飞向外太空</t>
-  </si>
-  <si>
-    <t>幸运时刻</t>
-  </si>
-  <si>
-    <t>不牢靠的按钮</t>
-  </si>
-  <si>
-    <t>找到最大的数</t>
-  </si>
-  <si>
-    <t>人机验证1</t>
-  </si>
-  <si>
-    <t>人机验证2</t>
-  </si>
-  <si>
-    <t>风力太大</t>
-  </si>
-  <si>
-    <t>翻页过关</t>
-  </si>
-  <si>
-    <t>基于气球关 点暂停</t>
-  </si>
-  <si>
-    <t>Loading加载</t>
-  </si>
-  <si>
-    <t>超重</t>
-  </si>
-  <si>
-    <t>是时候休息了</t>
-  </si>
-  <si>
-    <t>障眼法</t>
-  </si>
-  <si>
-    <t>按钮下的秘密</t>
-  </si>
-  <si>
-    <t>重新来过</t>
-  </si>
-  <si>
-    <t>去月球2</t>
-  </si>
-  <si>
-    <t>手忙脚乱</t>
-  </si>
-  <si>
-    <t>活动砖块</t>
-  </si>
-  <si>
-    <t>摩擦生热</t>
+    <t>关卡配置数据</t>
+  </si>
+  <si>
+    <t>关卡地图</t>
+  </si>
+  <si>
+    <t>Level001</t>
+  </si>
+  <si>
+    <t>Level_001</t>
+  </si>
+  <si>
+    <t>Level002</t>
+  </si>
+  <si>
+    <t>Level_002</t>
+  </si>
+  <si>
+    <t>Level003</t>
+  </si>
+  <si>
+    <t>Level004</t>
+  </si>
+  <si>
+    <t>Level005</t>
+  </si>
+  <si>
+    <t>Level006</t>
+  </si>
+  <si>
+    <t>Level007</t>
+  </si>
+  <si>
+    <t>Level008</t>
+  </si>
+  <si>
+    <t>Level009</t>
+  </si>
+  <si>
+    <t>Level010</t>
+  </si>
+  <si>
+    <t>Level011</t>
+  </si>
+  <si>
+    <t>Level012</t>
+  </si>
+  <si>
+    <t>Level013</t>
+  </si>
+  <si>
+    <t>Level014</t>
+  </si>
+  <si>
+    <t>Level015</t>
+  </si>
+  <si>
+    <t>Level016</t>
+  </si>
+  <si>
+    <t>Level017</t>
+  </si>
+  <si>
+    <t>Level018</t>
+  </si>
+  <si>
+    <t>Level019</t>
+  </si>
+  <si>
+    <t>Level020</t>
+  </si>
+  <si>
+    <t>Level021</t>
+  </si>
+  <si>
+    <t>Level022</t>
+  </si>
+  <si>
+    <t>Level023</t>
+  </si>
+  <si>
+    <t>Level024</t>
+  </si>
+  <si>
+    <t>Level025</t>
+  </si>
+  <si>
+    <t>Level026</t>
+  </si>
+  <si>
+    <t>Level027</t>
+  </si>
+  <si>
+    <t>Level028</t>
+  </si>
+  <si>
+    <t>Level029</t>
+  </si>
+  <si>
+    <t>Level030</t>
   </si>
 </sst>
 </file>
@@ -262,7 +208,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,12 +244,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -459,18 +399,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -815,58 +749,61 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -875,101 +812,92 @@
     <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -980,30 +908,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1316,690 +1220,437 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="9" style="3"/>
+    <col min="2" max="2" width="9" style="1"/>
     <col min="3" max="3" width="20.375" customWidth="1"/>
     <col min="4" max="4" width="21.25" customWidth="1"/>
     <col min="6" max="6" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6"/>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:7">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:7">
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:7">
+      <c r="B8" s="1">
         <v>3</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:7">
+      <c r="B9" s="1">
         <v>4</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="9"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:7">
+      <c r="B10" s="1">
         <v>5</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="7" t="s">
+      <c r="C10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:7">
+      <c r="B11" s="1">
         <v>6</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="4" t="s">
+      <c r="C11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="9"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:7">
+      <c r="B12" s="1">
         <v>7</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="9"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:7">
+      <c r="B13" s="1">
         <v>8</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C13" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="9"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:7">
+      <c r="B14" s="1">
         <v>9</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="C14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="10"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:7">
+      <c r="B15" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:7">
-      <c r="B6" s="3">
-        <v>1</v>
-      </c>
-      <c r="C6" s="10">
-        <v>10001</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="10"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:7">
+      <c r="B16" s="1">
         <v>11</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-    </row>
-    <row r="7" ht="16.5" spans="1:7">
-      <c r="B7" s="3">
-        <v>2</v>
-      </c>
-      <c r="C7" s="10">
-        <v>10002</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="9"/>
+    </row>
+    <row r="17" ht="16.5" spans="2:7">
+      <c r="B17" s="1">
         <v>12</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:7">
-      <c r="B8" s="3">
-        <v>3</v>
-      </c>
-      <c r="C8" s="10">
-        <v>10003</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="10"/>
+    </row>
+    <row r="18" ht="16.5" spans="2:7">
+      <c r="B18" s="1">
         <v>13</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-    </row>
-    <row r="9" ht="16.5" spans="1:7">
-      <c r="B9" s="3">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10">
-        <v>10006</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="9"/>
+    </row>
+    <row r="19" ht="16.5" spans="2:7">
+      <c r="B19" s="1">
         <v>14</v>
       </c>
-      <c r="G9" s="11"/>
-    </row>
-    <row r="10" ht="16.5" spans="1:7">
-      <c r="B10" s="3">
-        <v>5</v>
-      </c>
-      <c r="C10" s="10">
-        <v>10011</v>
-      </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="11"/>
-    </row>
-    <row r="11" ht="16.5" spans="1:7">
-      <c r="B11" s="3">
-        <v>6</v>
-      </c>
-      <c r="C11" s="10">
-        <v>10010</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="C19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="10"/>
+    </row>
+    <row r="20" ht="16.5" spans="2:7">
+      <c r="B20" s="1">
+        <v>15</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="9"/>
+    </row>
+    <row r="21" ht="16.5" spans="2:7">
+      <c r="B21" s="1">
         <v>16</v>
       </c>
-      <c r="G11" s="11"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:7">
-      <c r="B12" s="3">
-        <v>7</v>
-      </c>
-      <c r="C12" s="10">
-        <v>10004</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="10"/>
+    </row>
+    <row r="22" ht="16.5" spans="2:7">
+      <c r="B22" s="1">
         <v>17</v>
       </c>
-      <c r="G12" s="11"/>
-    </row>
-    <row r="13" ht="16.5" spans="1:7">
-      <c r="B13" s="3">
-        <v>8</v>
-      </c>
-      <c r="C13" s="10">
-        <v>10008</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="10"/>
+    </row>
+    <row r="23" ht="16.5" spans="2:7">
+      <c r="B23" s="1">
         <v>18</v>
       </c>
-      <c r="G13" s="11"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:7">
-      <c r="B14" s="3">
-        <v>9</v>
-      </c>
-      <c r="C14" s="10">
-        <v>10007</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="10"/>
+    </row>
+    <row r="24" ht="16.5" spans="2:7">
+      <c r="B24" s="1">
         <v>19</v>
       </c>
-      <c r="G14" s="12"/>
-    </row>
-    <row r="15" ht="16.5" spans="1:7">
-      <c r="B15" s="3">
-        <v>10</v>
-      </c>
-      <c r="C15" s="13">
-        <v>10042</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="C24" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="10"/>
+    </row>
+    <row r="25" ht="16.5" spans="2:7">
+      <c r="B25" s="1">
         <v>20</v>
       </c>
-      <c r="G15" s="12"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:7">
-      <c r="B16" s="3">
-        <v>11</v>
-      </c>
-      <c r="C16" s="14">
-        <v>10019</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C25" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="10"/>
+    </row>
+    <row r="26" ht="16.5" spans="2:7">
+      <c r="B26" s="1">
         <v>21</v>
       </c>
-      <c r="G16" s="11"/>
-    </row>
-    <row r="17" ht="16.5" spans="2:7">
-      <c r="B17" s="3">
-        <v>12</v>
-      </c>
-      <c r="C17" s="10">
-        <v>10009</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C26" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="10"/>
+    </row>
+    <row r="27" ht="16.5" spans="2:7">
+      <c r="B27" s="1">
         <v>22</v>
       </c>
-      <c r="G17" s="12"/>
-    </row>
-    <row r="18" ht="16.5" spans="2:7">
-      <c r="B18" s="3">
-        <v>13</v>
-      </c>
-      <c r="C18" s="14">
-        <v>10012</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="C27" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="10"/>
+    </row>
+    <row r="28" ht="16.5" spans="2:7">
+      <c r="B28" s="1">
         <v>23</v>
       </c>
-      <c r="G18" s="11"/>
-    </row>
-    <row r="19" ht="16.5" spans="2:7">
-      <c r="B19" s="3">
-        <v>14</v>
-      </c>
-      <c r="C19" s="14">
-        <v>10013</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C28" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="10"/>
+    </row>
+    <row r="29" ht="16.5" spans="2:7">
+      <c r="B29" s="1">
         <v>24</v>
       </c>
-      <c r="G19" s="12"/>
-    </row>
-    <row r="20" ht="16.5" spans="2:7">
-      <c r="B20" s="3">
-        <v>15</v>
-      </c>
-      <c r="C20" s="14">
-        <v>10014</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="C29" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="9"/>
+    </row>
+    <row r="30" ht="16.5" spans="2:7">
+      <c r="B30" s="1">
         <v>25</v>
       </c>
-      <c r="G20" s="11"/>
-    </row>
-    <row r="21" ht="16.5" spans="2:7">
-      <c r="B21" s="3">
-        <v>16</v>
-      </c>
-      <c r="C21" s="14">
-        <v>10031</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="C30" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="10"/>
+    </row>
+    <row r="31" ht="16.5" spans="2:7">
+      <c r="B31" s="1">
         <v>26</v>
       </c>
-      <c r="G21" s="12"/>
-    </row>
-    <row r="22" ht="16.5" spans="2:7">
-      <c r="B22" s="3">
-        <v>17</v>
-      </c>
-      <c r="C22" s="14">
-        <v>10036</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="C31" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="10"/>
+    </row>
+    <row r="32" ht="16.5" spans="2:7">
+      <c r="B32" s="1">
         <v>27</v>
       </c>
-      <c r="G22" s="12"/>
-    </row>
-    <row r="23" ht="16.5" spans="2:7">
-      <c r="B23" s="3">
-        <v>18</v>
-      </c>
-      <c r="C23" s="14">
-        <v>10017</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="C32" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="10"/>
+    </row>
+    <row r="33" ht="16.5" spans="2:7">
+      <c r="B33" s="1">
         <v>28</v>
       </c>
-      <c r="G23" s="12"/>
-    </row>
-    <row r="24" ht="16.5" spans="2:7">
-      <c r="B24" s="3">
-        <v>19</v>
-      </c>
-      <c r="C24" s="14">
-        <v>10021</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C33" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="10"/>
+    </row>
+    <row r="34" ht="16.5" spans="2:7">
+      <c r="B34" s="1">
         <v>29</v>
       </c>
-      <c r="G24" s="12"/>
-    </row>
-    <row r="25" ht="16.5" spans="2:7">
-      <c r="B25" s="3">
-        <v>20</v>
-      </c>
-      <c r="C25" s="14">
-        <v>10015</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="C34" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="10"/>
+    </row>
+    <row r="35" ht="16.5" spans="2:7">
+      <c r="B35" s="1">
         <v>30</v>
       </c>
-      <c r="G25" s="12"/>
-    </row>
-    <row r="26" ht="16.5" spans="2:7">
-      <c r="B26" s="3">
-        <v>21</v>
-      </c>
-      <c r="C26" s="14">
-        <v>10018</v>
-      </c>
-      <c r="D26" t="s">
-        <v>31</v>
-      </c>
-      <c r="G26" s="12"/>
-    </row>
-    <row r="27" ht="16.5" spans="2:7">
-      <c r="B27" s="3">
-        <v>22</v>
-      </c>
-      <c r="C27" s="14">
-        <v>10020</v>
-      </c>
-      <c r="D27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27" s="12"/>
-    </row>
-    <row r="28" ht="16.5" spans="2:7">
-      <c r="B28" s="3">
-        <v>23</v>
-      </c>
-      <c r="C28" s="14">
-        <v>10016</v>
-      </c>
-      <c r="D28" t="s">
-        <v>33</v>
-      </c>
-      <c r="G28" s="12"/>
-    </row>
-    <row r="29" ht="16.5" spans="2:7">
-      <c r="B29" s="3">
-        <v>24</v>
-      </c>
-      <c r="C29" s="14">
-        <v>10027</v>
-      </c>
-      <c r="D29" t="s">
-        <v>34</v>
-      </c>
-      <c r="G29" s="11"/>
-    </row>
-    <row r="30" ht="16.5" spans="2:7">
-      <c r="B30" s="3">
-        <v>25</v>
-      </c>
-      <c r="C30" s="10">
-        <v>10022</v>
-      </c>
-      <c r="D30" t="s">
-        <v>35</v>
-      </c>
-      <c r="G30" s="12"/>
-    </row>
-    <row r="31" ht="16.5" spans="2:7">
-      <c r="B31" s="3">
-        <v>26</v>
-      </c>
-      <c r="C31" s="14">
-        <v>10024</v>
-      </c>
-      <c r="D31" t="s">
-        <v>36</v>
-      </c>
-      <c r="G31" s="12"/>
-    </row>
-    <row r="32" ht="16.5" spans="2:7">
-      <c r="B32" s="3">
-        <v>27</v>
-      </c>
-      <c r="C32" s="14">
-        <v>10023</v>
-      </c>
-      <c r="D32" t="s">
-        <v>37</v>
-      </c>
-      <c r="G32" s="12"/>
-    </row>
-    <row r="33" ht="16.5" spans="2:7">
-      <c r="B33" s="3">
-        <v>28</v>
-      </c>
-      <c r="C33" s="14">
-        <v>10029</v>
-      </c>
-      <c r="D33" t="s">
-        <v>38</v>
-      </c>
-      <c r="G33" s="12"/>
-    </row>
-    <row r="34" ht="16.5" spans="2:7">
-      <c r="B34" s="3">
-        <v>29</v>
-      </c>
-      <c r="C34" s="14">
-        <v>10026</v>
-      </c>
-      <c r="D34" t="s">
-        <v>39</v>
-      </c>
-      <c r="G34" s="12"/>
-    </row>
-    <row r="35" ht="16.5" spans="2:7">
-      <c r="B35" s="3">
-        <v>30</v>
-      </c>
-      <c r="C35" s="14">
-        <v>10028</v>
+      <c r="C35" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="D35" t="s">
-        <v>40</v>
-      </c>
-      <c r="G35" s="12"/>
-    </row>
-    <row r="36" ht="16.5" spans="2:7">
-      <c r="B36" s="3">
-        <v>31</v>
-      </c>
-      <c r="C36" s="14">
-        <v>10025</v>
-      </c>
-      <c r="D36" t="s">
-        <v>41</v>
-      </c>
-      <c r="G36" s="12"/>
-    </row>
-    <row r="37" ht="16.5" spans="2:7">
-      <c r="B37" s="3">
-        <v>32</v>
-      </c>
-      <c r="C37" s="14">
-        <v>10030</v>
-      </c>
-      <c r="D37" t="s">
-        <v>42</v>
-      </c>
-      <c r="G37" s="12"/>
-    </row>
-    <row r="38" ht="16.5" spans="2:7">
-      <c r="B38" s="3">
-        <v>33</v>
-      </c>
-      <c r="C38" s="14">
-        <v>10032</v>
-      </c>
-      <c r="D38" t="s">
-        <v>43</v>
-      </c>
-      <c r="G38" s="12"/>
-    </row>
-    <row r="39" ht="16.5" spans="2:7">
-      <c r="B39" s="3">
-        <v>34</v>
-      </c>
-      <c r="C39" s="14">
-        <v>10033</v>
-      </c>
-      <c r="D39" t="s">
-        <v>44</v>
-      </c>
-      <c r="G39" s="12"/>
-    </row>
-    <row r="40" ht="16.5" spans="2:7">
-      <c r="B40" s="3">
-        <v>35</v>
-      </c>
-      <c r="C40" s="14">
-        <v>10034</v>
-      </c>
-      <c r="D40" t="s">
-        <v>45</v>
-      </c>
-      <c r="G40" s="12"/>
-    </row>
-    <row r="41" ht="16.5" spans="2:7">
-      <c r="B41" s="3">
-        <v>36</v>
-      </c>
-      <c r="C41" s="14">
-        <v>10035</v>
-      </c>
-      <c r="D41" t="s">
-        <v>46</v>
-      </c>
-      <c r="G41" s="12"/>
-    </row>
-    <row r="42" s="1" customFormat="1" ht="16.5" spans="2:7">
-      <c r="B42" s="15">
-        <v>37</v>
-      </c>
-      <c r="C42" s="15">
-        <v>10037</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" ht="16.5" spans="2:7">
-      <c r="B43" s="16">
-        <v>38</v>
-      </c>
-      <c r="C43" s="16">
-        <v>10038</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="16.5" spans="2:7">
-      <c r="B44" s="16">
-        <v>39</v>
-      </c>
-      <c r="C44" s="17">
-        <v>10039</v>
-      </c>
-      <c r="D44" s="17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="16.5" spans="2:7">
-      <c r="B45" s="16">
-        <v>40</v>
-      </c>
-      <c r="C45" s="18">
-        <v>10040</v>
-      </c>
-      <c r="D45" s="18" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="16.5" spans="2:7">
-      <c r="B46" s="16">
-        <v>41</v>
-      </c>
-      <c r="C46" s="18">
-        <v>10041</v>
-      </c>
-      <c r="D46" s="19" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" ht="16.5" spans="2:7">
-      <c r="B47" s="16">
-        <v>42</v>
-      </c>
-      <c r="C47" s="16">
-        <v>10042</v>
-      </c>
-      <c r="D47" s="19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" ht="16.5" spans="2:7">
-      <c r="B48" s="16">
-        <v>43</v>
-      </c>
-      <c r="C48" s="16">
-        <v>10043</v>
-      </c>
-      <c r="D48" s="19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="49" s="2" customFormat="1" ht="16.5" spans="2:4">
-      <c r="B49" s="16">
-        <v>44</v>
-      </c>
-      <c r="C49" s="20">
-        <v>10044</v>
-      </c>
-      <c r="D49" s="19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="50" s="2" customFormat="1" ht="16.5" spans="2:4">
-      <c r="B50" s="16">
-        <v>45</v>
-      </c>
-      <c r="C50" s="16">
-        <v>10045</v>
-      </c>
-      <c r="D50" s="19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="51" s="2" customFormat="1" ht="16.5" spans="2:4">
-      <c r="B51" s="16">
-        <v>46</v>
-      </c>
-      <c r="C51" s="16">
-        <v>10046</v>
-      </c>
-      <c r="D51" s="19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="52" s="2" customFormat="1" ht="16.5" spans="2:4">
-      <c r="B52" s="16">
-        <v>47</v>
-      </c>
-      <c r="C52" s="16">
-        <v>10047</v>
-      </c>
-      <c r="D52" s="19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="53" s="2" customFormat="1" ht="16.5" spans="2:4">
-      <c r="B53" s="16">
-        <v>48</v>
-      </c>
-      <c r="C53" s="16">
-        <v>10048</v>
-      </c>
-    </row>
-    <row r="54" s="2" customFormat="1" ht="16.5" spans="2:4">
-      <c r="B54" s="16">
-        <v>49</v>
-      </c>
-      <c r="C54" s="20">
-        <v>10049</v>
-      </c>
-      <c r="D54" s="19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="55" s="2" customFormat="1" ht="16.5" spans="2:4">
-      <c r="B55" s="16">
-        <v>50</v>
-      </c>
-      <c r="C55" s="16">
-        <v>10050</v>
-      </c>
-      <c r="D55" s="19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="56" s="2" customFormat="1" ht="16.5" spans="2:4">
-      <c r="B56" s="16">
-        <v>51</v>
-      </c>
-      <c r="C56" s="16">
-        <v>10051</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" ht="16.5" spans="2:4">
-      <c r="B57" s="16">
-        <v>52</v>
-      </c>
-      <c r="C57" s="15">
-        <v>10052</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>61</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G35" s="10"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D47" r:id="rId3" display="Loading加载" tooltip="https://scnmrtumk0zm.feishu.cn/wiki/X7MawRHVLisJfAkRzS9cDoyEn1f"/>
-    <hyperlink ref="D48" r:id="rId4" display="超重" tooltip="https://scnmrtumk0zm.feishu.cn/wiki/QEbHwdNCRi03FvkMSxYcTr9knHd"/>
-    <hyperlink ref="D49" r:id="rId5" display="是时候休息了" tooltip="https://scnmrtumk0zm.feishu.cn/wiki/NvGWwhp9EiOKVPk1oE2czx4onad"/>
-    <hyperlink ref="D50" r:id="rId6" display="障眼法" tooltip="https://scnmrtumk0zm.feishu.cn/wiki/TWq4wlMF9imR4akW3M8cFQ9Nndf"/>
-    <hyperlink ref="D51" r:id="rId7" display="按钮下的秘密" tooltip="https://scnmrtumk0zm.feishu.cn/wiki/Z3AGwYOfGiyAOkkR0vbcgkUInWd"/>
-    <hyperlink ref="D52" r:id="rId8" display="重新来过" tooltip="https://scnmrtumk0zm.feishu.cn/wiki/PcNcwAo9biYPI6kUbHXc1zOInJb"/>
-    <hyperlink ref="D54" r:id="rId9" display="去月球2" tooltip="https://scnmrtumk0zm.feishu.cn/wiki/P9HYwFiSTiWQ7Kk31YVcIy1lnBc"/>
-    <hyperlink ref="D55" r:id="rId10" display="手忙脚乱" tooltip="https://scnmrtumk0zm.feishu.cn/wiki/XrPKwG8qcitNynkEhavcWIVfnCc"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/SheepDemo/Luban/Configs/Datas/#LevelSort.xlsx
+++ b/SheepDemo/Luban/Configs/Datas/#LevelSort.xlsx
@@ -111,10 +111,10 @@
     <t>Level002</t>
   </si>
   <si>
+    <t>Level003</t>
+  </si>
+  <si>
     <t>Level_002</t>
-  </si>
-  <si>
-    <t>Level003</t>
   </si>
   <si>
     <t>Level004</t>
@@ -388,12 +388,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1308,7 +1308,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
@@ -1318,10 +1318,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
@@ -1334,7 +1334,7 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" s="9"/>
     </row>
@@ -1346,7 +1346,7 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G10" s="9"/>
     </row>
@@ -1358,7 +1358,7 @@
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G11" s="9"/>
     </row>
@@ -1370,7 +1370,7 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G12" s="9"/>
     </row>
@@ -1382,7 +1382,7 @@
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G13" s="9"/>
     </row>
@@ -1394,7 +1394,7 @@
         <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G14" s="10"/>
     </row>
@@ -1406,7 +1406,7 @@
         <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G15" s="10"/>
     </row>
@@ -1418,7 +1418,7 @@
         <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" s="9"/>
     </row>
@@ -1430,7 +1430,7 @@
         <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" s="10"/>
     </row>
@@ -1442,7 +1442,7 @@
         <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G18" s="9"/>
     </row>
@@ -1454,7 +1454,7 @@
         <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G19" s="10"/>
     </row>
@@ -1466,7 +1466,7 @@
         <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" s="9"/>
     </row>
@@ -1478,7 +1478,7 @@
         <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G21" s="10"/>
     </row>
@@ -1490,7 +1490,7 @@
         <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" s="10"/>
     </row>
@@ -1502,7 +1502,7 @@
         <v>31</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G23" s="10"/>
     </row>
@@ -1514,7 +1514,7 @@
         <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G24" s="10"/>
     </row>
@@ -1526,7 +1526,7 @@
         <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G25" s="10"/>
     </row>
@@ -1538,7 +1538,7 @@
         <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G26" s="10"/>
     </row>
@@ -1550,7 +1550,7 @@
         <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G27" s="10"/>
     </row>
@@ -1562,7 +1562,7 @@
         <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G28" s="10"/>
     </row>
@@ -1574,7 +1574,7 @@
         <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G29" s="9"/>
     </row>
@@ -1586,7 +1586,7 @@
         <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G30" s="10"/>
     </row>
@@ -1598,7 +1598,7 @@
         <v>39</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G31" s="10"/>
     </row>
@@ -1610,7 +1610,7 @@
         <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G32" s="10"/>
     </row>
@@ -1622,7 +1622,7 @@
         <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G33" s="10"/>
     </row>
@@ -1634,7 +1634,7 @@
         <v>42</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G34" s="10"/>
     </row>
@@ -1646,7 +1646,7 @@
         <v>43</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G35" s="10"/>
     </row>

--- a/SheepDemo/Luban/Configs/Datas/#LevelSort.xlsx
+++ b/SheepDemo/Luban/Configs/Datas/#LevelSort.xlsx
@@ -102,100 +102,100 @@
     <t>关卡地图</t>
   </si>
   <si>
-    <t>Level001</t>
+    <t>level001</t>
   </si>
   <si>
     <t>Level_001</t>
   </si>
   <si>
-    <t>Level002</t>
-  </si>
-  <si>
-    <t>Level003</t>
+    <t>level002</t>
+  </si>
+  <si>
+    <t>level003</t>
   </si>
   <si>
     <t>Level_002</t>
   </si>
   <si>
-    <t>Level004</t>
-  </si>
-  <si>
-    <t>Level005</t>
-  </si>
-  <si>
-    <t>Level006</t>
-  </si>
-  <si>
-    <t>Level007</t>
-  </si>
-  <si>
-    <t>Level008</t>
-  </si>
-  <si>
-    <t>Level009</t>
-  </si>
-  <si>
-    <t>Level010</t>
-  </si>
-  <si>
-    <t>Level011</t>
-  </si>
-  <si>
-    <t>Level012</t>
-  </si>
-  <si>
-    <t>Level013</t>
-  </si>
-  <si>
-    <t>Level014</t>
-  </si>
-  <si>
-    <t>Level015</t>
-  </si>
-  <si>
-    <t>Level016</t>
-  </si>
-  <si>
-    <t>Level017</t>
-  </si>
-  <si>
-    <t>Level018</t>
-  </si>
-  <si>
-    <t>Level019</t>
-  </si>
-  <si>
-    <t>Level020</t>
-  </si>
-  <si>
-    <t>Level021</t>
-  </si>
-  <si>
-    <t>Level022</t>
-  </si>
-  <si>
-    <t>Level023</t>
-  </si>
-  <si>
-    <t>Level024</t>
-  </si>
-  <si>
-    <t>Level025</t>
-  </si>
-  <si>
-    <t>Level026</t>
-  </si>
-  <si>
-    <t>Level027</t>
-  </si>
-  <si>
-    <t>Level028</t>
-  </si>
-  <si>
-    <t>Level029</t>
-  </si>
-  <si>
-    <t>Level030</t>
+    <t>level004</t>
+  </si>
+  <si>
+    <t>level005</t>
+  </si>
+  <si>
+    <t>level006</t>
+  </si>
+  <si>
+    <t>level007</t>
+  </si>
+  <si>
+    <t>level008</t>
+  </si>
+  <si>
+    <t>level009</t>
+  </si>
+  <si>
+    <t>level010</t>
+  </si>
+  <si>
+    <t>level011</t>
+  </si>
+  <si>
+    <t>level012</t>
+  </si>
+  <si>
+    <t>level013</t>
+  </si>
+  <si>
+    <t>level014</t>
+  </si>
+  <si>
+    <t>level015</t>
+  </si>
+  <si>
+    <t>level016</t>
+  </si>
+  <si>
+    <t>level017</t>
+  </si>
+  <si>
+    <t>level018</t>
+  </si>
+  <si>
+    <t>level019</t>
+  </si>
+  <si>
+    <t>level020</t>
+  </si>
+  <si>
+    <t>level021</t>
+  </si>
+  <si>
+    <t>level022</t>
+  </si>
+  <si>
+    <t>level023</t>
+  </si>
+  <si>
+    <t>level024</t>
+  </si>
+  <si>
+    <t>level025</t>
+  </si>
+  <si>
+    <t>level026</t>
+  </si>
+  <si>
+    <t>level027</t>
+  </si>
+  <si>
+    <t>level028</t>
+  </si>
+  <si>
+    <t>level029</t>
+  </si>
+  <si>
+    <t>level030</t>
   </si>
 </sst>
 </file>
@@ -388,12 +388,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/SheepDemo/Luban/Configs/Datas/#LevelSort.xlsx
+++ b/SheepDemo/Luban/Configs/Datas/#LevelSort.xlsx
@@ -111,10 +111,10 @@
     <t>level002</t>
   </si>
   <si>
+    <t>Level_002</t>
+  </si>
+  <si>
     <t>level003</t>
-  </si>
-  <si>
-    <t>Level_002</t>
   </si>
   <si>
     <t>level004</t>
@@ -1308,7 +1308,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
@@ -1318,10 +1318,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
@@ -1334,7 +1334,7 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G9" s="9"/>
     </row>
@@ -1346,7 +1346,7 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G10" s="9"/>
     </row>
@@ -1358,7 +1358,7 @@
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G11" s="9"/>
     </row>
@@ -1370,7 +1370,7 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G12" s="9"/>
     </row>
@@ -1382,7 +1382,7 @@
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G13" s="9"/>
     </row>
@@ -1394,7 +1394,7 @@
         <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G14" s="10"/>
     </row>
@@ -1406,7 +1406,7 @@
         <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G15" s="10"/>
     </row>
@@ -1418,7 +1418,7 @@
         <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G16" s="9"/>
     </row>
@@ -1430,7 +1430,7 @@
         <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G17" s="10"/>
     </row>
@@ -1442,7 +1442,7 @@
         <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" s="9"/>
     </row>
@@ -1454,7 +1454,7 @@
         <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G19" s="10"/>
     </row>
@@ -1466,7 +1466,7 @@
         <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G20" s="9"/>
     </row>
@@ -1478,7 +1478,7 @@
         <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G21" s="10"/>
     </row>
@@ -1490,7 +1490,7 @@
         <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22" s="10"/>
     </row>
@@ -1502,7 +1502,7 @@
         <v>31</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G23" s="10"/>
     </row>
@@ -1514,7 +1514,7 @@
         <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G24" s="10"/>
     </row>
@@ -1526,7 +1526,7 @@
         <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25" s="10"/>
     </row>
@@ -1538,7 +1538,7 @@
         <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G26" s="10"/>
     </row>
@@ -1550,7 +1550,7 @@
         <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G27" s="10"/>
     </row>
@@ -1562,7 +1562,7 @@
         <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G28" s="10"/>
     </row>
@@ -1574,7 +1574,7 @@
         <v>37</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G29" s="9"/>
     </row>
@@ -1586,7 +1586,7 @@
         <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G30" s="10"/>
     </row>
@@ -1598,7 +1598,7 @@
         <v>39</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G31" s="10"/>
     </row>
@@ -1610,7 +1610,7 @@
         <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G32" s="10"/>
     </row>
@@ -1622,7 +1622,7 @@
         <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G33" s="10"/>
     </row>
@@ -1634,7 +1634,7 @@
         <v>42</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G34" s="10"/>
     </row>
@@ -1646,7 +1646,7 @@
         <v>43</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G35" s="10"/>
     </row>
